--- a/ANET.xlsx
+++ b/ANET.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F58FC134-B45A-47B4-84EF-B028710DBA6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BA292F0-77D2-4161-942F-0636C376DCB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" activeTab="1" xr2:uid="{9C11DE66-4D28-4FC9-B304-9B363AD3030B}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{9C11DE66-4D28-4FC9-B304-9B363AD3030B}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="53">
   <si>
     <t>ANET</t>
   </si>
@@ -198,21 +198,61 @@
   <si>
     <t>Tax Rate</t>
   </si>
+  <si>
+    <t>CEO:</t>
+  </si>
+  <si>
+    <t>Jayshree V. Ullal</t>
+  </si>
+  <si>
+    <t>Q325</t>
+  </si>
+  <si>
+    <t>Q125</t>
+  </si>
+  <si>
+    <t>Q225</t>
+  </si>
+  <si>
+    <t>Q425</t>
+  </si>
+  <si>
+    <t>Software-driven cloud networking solutions</t>
+  </si>
+  <si>
+    <t>Products</t>
+  </si>
+  <si>
+    <t>high-speed, low-latency Ethernet switches and routing platform</t>
+  </si>
+  <si>
+    <t>Software:</t>
+  </si>
+  <si>
+    <t>Exentsible Operating Syste</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
+    <numFmt numFmtId="165" formatCode="#,##0;\(#,##0\)"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -262,6 +302,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -282,22 +329,29 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -634,13 +688,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD30EF89-FC35-4936-8B67-82EC24CE9A5D}">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4" style="2" customWidth="1"/>
-    <col min="2" max="8" width="9.140625" style="2"/>
-    <col min="9" max="9" width="10.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="2"/>
+    <col min="2" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
@@ -655,20 +707,19 @@
       <c r="H2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="2">
-        <v>119.69</v>
+      <c r="I2" s="11">
+        <v>133.80000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="H3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="3">
-        <f>314.939883*3</f>
-        <v>944.81964900000003</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>10</v>
+      <c r="I3" s="11">
+        <v>1259.2850699999999</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -678,49 +729,83 @@
       <c r="H4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="11">
         <f>+I2*I3</f>
-        <v>113085.46378881</v>
+        <v>168492.342366</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="5" t="s">
         <v>3</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="3">
-        <f>3175.139+4253.249</f>
-        <v>7428.3879999999999</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>10</v>
+      <c r="I5" s="11">
+        <f>2326.6+7779.6</f>
+        <v>10106.200000000001</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="H6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="11">
         <v>0</v>
       </c>
-      <c r="J6" s="4" t="s">
-        <v>10</v>
+      <c r="J6" s="12" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="H7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I7" s="11">
         <f>+I4+I6-I5</f>
-        <v>105657.07578880999</v>
+        <v>158386.14236599999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B8" s="10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B9" s="14" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B10" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B11" s="10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B12" s="10" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B5" r:id="rId1" xr:uid="{00BBE166-D7DD-464F-9B2E-3C6EBB86B252}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -764,6 +849,18 @@
       <c r="J2" s="4" t="s">
         <v>18</v>
       </c>
+      <c r="K2" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="L2" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="M2" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="N2" s="12" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="3" spans="1:66" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
@@ -775,15 +872,25 @@
         <v>1285.548</v>
       </c>
       <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
+      <c r="G3" s="3">
+        <v>1328.8</v>
+      </c>
+      <c r="H3" s="3">
+        <v>1423.3</v>
+      </c>
       <c r="I3" s="3">
         <v>1523.807</v>
       </c>
       <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
+      <c r="K3" s="3">
+        <v>1692.5</v>
+      </c>
+      <c r="L3" s="3">
+        <v>1877</v>
+      </c>
+      <c r="M3" s="3">
+        <v>1911.7</v>
+      </c>
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
@@ -848,15 +955,25 @@
         <v>223.90799999999999</v>
       </c>
       <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
+      <c r="G4" s="3">
+        <v>242.6</v>
+      </c>
+      <c r="H4" s="3">
+        <v>267.10000000000002</v>
+      </c>
       <c r="I4" s="3">
         <v>287.12900000000002</v>
       </c>
       <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
+      <c r="K4" s="3">
+        <v>312.3</v>
+      </c>
+      <c r="L4" s="3">
+        <v>327.8</v>
+      </c>
+      <c r="M4" s="3">
+        <v>396.6</v>
+      </c>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
@@ -933,24 +1050,36 @@
       </c>
       <c r="G5" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1571.3999999999999</v>
       </c>
       <c r="H5" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1690.4</v>
       </c>
       <c r="I5" s="7">
         <f>+I3+I4</f>
         <v>1810.9360000000001</v>
       </c>
       <c r="J5" s="7">
-        <f t="shared" ref="J5" si="1">+J3+J4</f>
+        <f t="shared" ref="J5:N5" si="1">+J3+J4</f>
         <v>0</v>
       </c>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
+      <c r="K5" s="7">
+        <f t="shared" si="1"/>
+        <v>2004.8</v>
+      </c>
+      <c r="L5" s="7">
+        <f t="shared" si="1"/>
+        <v>2204.8000000000002</v>
+      </c>
+      <c r="M5" s="7">
+        <f t="shared" si="1"/>
+        <v>2308.3000000000002</v>
+      </c>
+      <c r="N5" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
@@ -1014,15 +1143,25 @@
         <v>522.86599999999999</v>
       </c>
       <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
+      <c r="G6" s="3">
+        <v>521.70000000000005</v>
+      </c>
+      <c r="H6" s="3">
+        <v>540.4</v>
+      </c>
       <c r="I6" s="3">
         <v>593.34299999999996</v>
       </c>
       <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
+      <c r="K6" s="3">
+        <v>672.7</v>
+      </c>
+      <c r="L6" s="3">
+        <v>707.3</v>
+      </c>
+      <c r="M6" s="3">
+        <v>745.5</v>
+      </c>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
@@ -1087,15 +1226,25 @@
         <v>44.170999999999999</v>
       </c>
       <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
+      <c r="G7" s="3">
+        <v>48.3</v>
+      </c>
+      <c r="H7" s="3">
+        <v>52.8</v>
+      </c>
       <c r="I7" s="3">
         <v>55.875999999999998</v>
       </c>
       <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
+      <c r="K7" s="3">
+        <v>56</v>
+      </c>
+      <c r="L7" s="3">
+        <v>58.9</v>
+      </c>
+      <c r="M7" s="3">
+        <v>72.599999999999994</v>
+      </c>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
@@ -1172,24 +1321,36 @@
       </c>
       <c r="G8" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1001.3999999999999</v>
       </c>
       <c r="H8" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1097.2000000000003</v>
       </c>
       <c r="I8" s="3">
         <f>+I5-SUM(I6:I7)</f>
         <v>1161.7170000000001</v>
       </c>
       <c r="J8" s="3">
-        <f t="shared" ref="J8" si="3">+J5-SUM(J6:J7)</f>
+        <f t="shared" ref="J8:N8" si="3">+J5-SUM(J6:J7)</f>
         <v>0</v>
       </c>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
+      <c r="K8" s="3">
+        <f t="shared" si="3"/>
+        <v>1276.0999999999999</v>
+      </c>
+      <c r="L8" s="3">
+        <f t="shared" si="3"/>
+        <v>1438.6000000000004</v>
+      </c>
+      <c r="M8" s="3">
+        <f t="shared" si="3"/>
+        <v>1490.2000000000003</v>
+      </c>
+      <c r="N8" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
@@ -1253,15 +1414,25 @@
         <v>212.35300000000001</v>
       </c>
       <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
+      <c r="G9" s="3">
+        <v>208.4</v>
+      </c>
+      <c r="H9" s="3">
+        <v>267.5</v>
+      </c>
       <c r="I9" s="3">
         <v>235.82400000000001</v>
       </c>
       <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
+      <c r="K9" s="3">
+        <v>266.39999999999998</v>
+      </c>
+      <c r="L9" s="3">
+        <v>296.5</v>
+      </c>
+      <c r="M9" s="3">
+        <v>326</v>
+      </c>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
@@ -1326,15 +1497,25 @@
         <v>102.033</v>
       </c>
       <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
+      <c r="G10" s="3">
+        <v>105.1</v>
+      </c>
+      <c r="H10" s="3">
+        <v>104.4</v>
+      </c>
       <c r="I10" s="3">
         <v>106.83199999999999</v>
       </c>
       <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
+      <c r="K10" s="3">
+        <v>116.6</v>
+      </c>
+      <c r="L10" s="3">
+        <v>126.5</v>
+      </c>
+      <c r="M10" s="3">
+        <v>151.19999999999999</v>
+      </c>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
@@ -1399,15 +1580,25 @@
         <v>25.338000000000001</v>
       </c>
       <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
+      <c r="G11" s="3">
+        <v>27.7</v>
+      </c>
+      <c r="H11" s="3">
+        <v>25.7</v>
+      </c>
       <c r="I11" s="3">
         <v>33.811</v>
       </c>
       <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
+      <c r="K11" s="3">
+        <v>34.299999999999997</v>
+      </c>
+      <c r="L11" s="3">
+        <v>29.4</v>
+      </c>
+      <c r="M11" s="3">
+        <v>34.799999999999997</v>
+      </c>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
@@ -1484,24 +1675,36 @@
       </c>
       <c r="G12" s="3">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>660.19999999999982</v>
       </c>
       <c r="H12" s="3">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>699.60000000000036</v>
       </c>
       <c r="I12" s="3">
         <f>+I8-SUM(I9:I11)</f>
         <v>785.25000000000011</v>
       </c>
       <c r="J12" s="3">
-        <f t="shared" ref="J12" si="5">+J8-SUM(J9:J11)</f>
+        <f t="shared" ref="J12:N12" si="5">+J8-SUM(J9:J11)</f>
         <v>0</v>
       </c>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
+      <c r="K12" s="3">
+        <f t="shared" si="5"/>
+        <v>858.8</v>
+      </c>
+      <c r="L12" s="3">
+        <f t="shared" si="5"/>
+        <v>986.20000000000039</v>
+      </c>
+      <c r="M12" s="3">
+        <f t="shared" si="5"/>
+        <v>978.20000000000027</v>
+      </c>
+      <c r="N12" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
@@ -1565,15 +1768,25 @@
         <v>41.814999999999998</v>
       </c>
       <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
+      <c r="G13" s="3">
+        <v>62.6</v>
+      </c>
+      <c r="H13" s="3">
+        <v>70.8</v>
+      </c>
       <c r="I13" s="3">
         <v>97.66</v>
       </c>
       <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
+      <c r="K13" s="3">
+        <v>96.2</v>
+      </c>
+      <c r="L13" s="3">
+        <v>94</v>
+      </c>
+      <c r="M13" s="3">
+        <v>98.9</v>
+      </c>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
@@ -1650,24 +1863,36 @@
       </c>
       <c r="G14" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>722.79999999999984</v>
       </c>
       <c r="H14" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>770.40000000000032</v>
       </c>
       <c r="I14" s="3">
         <f>+I12+I13</f>
         <v>882.91000000000008</v>
       </c>
       <c r="J14" s="3">
-        <f t="shared" ref="J14" si="7">+J12+J13</f>
+        <f t="shared" ref="J14:N14" si="7">+J12+J13</f>
         <v>0</v>
       </c>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
+      <c r="K14" s="3">
+        <f t="shared" si="7"/>
+        <v>955</v>
+      </c>
+      <c r="L14" s="3">
+        <f t="shared" si="7"/>
+        <v>1080.2000000000003</v>
+      </c>
+      <c r="M14" s="3">
+        <f t="shared" si="7"/>
+        <v>1077.1000000000004</v>
+      </c>
+      <c r="N14" s="3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
@@ -1731,15 +1956,25 @@
         <v>99.183000000000007</v>
       </c>
       <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
+      <c r="G15" s="3">
+        <v>85.1</v>
+      </c>
+      <c r="H15" s="3">
+        <v>105</v>
+      </c>
       <c r="I15" s="3">
         <v>134.97200000000001</v>
       </c>
       <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
+      <c r="K15" s="3">
+        <v>141.19999999999999</v>
+      </c>
+      <c r="L15" s="3">
+        <v>191.4</v>
+      </c>
+      <c r="M15" s="3">
+        <v>224.1</v>
+      </c>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
@@ -1816,24 +2051,36 @@
       </c>
       <c r="G16" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>637.69999999999982</v>
       </c>
       <c r="H16" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>665.40000000000032</v>
       </c>
       <c r="I16" s="3">
         <f>+I14-I15</f>
         <v>747.9380000000001</v>
       </c>
       <c r="J16" s="3">
-        <f t="shared" ref="J16" si="9">+J14-J15</f>
+        <f t="shared" ref="J16:N16" si="9">+J14-J15</f>
         <v>0</v>
       </c>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
+      <c r="K16" s="3">
+        <f t="shared" si="9"/>
+        <v>813.8</v>
+      </c>
+      <c r="L16" s="3">
+        <f t="shared" si="9"/>
+        <v>888.8000000000003</v>
+      </c>
+      <c r="M16" s="3">
+        <f t="shared" si="9"/>
+        <v>853.00000000000034</v>
+      </c>
+      <c r="N16" s="3">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
@@ -1973,26 +2220,38 @@
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G18" s="8" t="e">
+      <c r="G18" s="8">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H18" s="8" t="e">
+        <v>0.50930436866064999</v>
+      </c>
+      <c r="H18" s="8">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>0.5302837105514826</v>
       </c>
       <c r="I18" s="8">
         <f>+I16/I19</f>
         <v>2.3783173599760876</v>
       </c>
       <c r="J18" s="8" t="e">
-        <f t="shared" ref="J18" si="11">+J16/J19</f>
+        <f t="shared" ref="J18:N18" si="11">+J16/J19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3"/>
+      <c r="K18" s="8">
+        <f t="shared" si="11"/>
+        <v>0.64587301587301582</v>
+      </c>
+      <c r="L18" s="8">
+        <f t="shared" si="11"/>
+        <v>0.70747432937992549</v>
+      </c>
+      <c r="M18" s="8">
+        <f t="shared" si="11"/>
+        <v>0.67806041335453127</v>
+      </c>
+      <c r="N18" s="8" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
@@ -2056,15 +2315,25 @@
         <v>310.185</v>
       </c>
       <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
+      <c r="G19" s="3">
+        <v>1252.0999999999999</v>
+      </c>
+      <c r="H19" s="3">
+        <v>1254.8</v>
+      </c>
       <c r="I19" s="3">
         <v>314.48200000000003</v>
       </c>
       <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
+      <c r="K19" s="3">
+        <v>1260</v>
+      </c>
+      <c r="L19" s="3">
+        <v>1256.3</v>
+      </c>
+      <c r="M19" s="3">
+        <v>1258</v>
+      </c>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
@@ -2206,13 +2475,25 @@
         <v>0.18533652574621873</v>
       </c>
       <c r="J21" s="9" t="e">
-        <f t="shared" ref="J21:J23" si="13">+J3/F3-1</f>
+        <f t="shared" ref="J21:N23" si="13">+J3/F3-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="3"/>
+      <c r="K21" s="9">
+        <f t="shared" si="13"/>
+        <v>0.27370559903672498</v>
+      </c>
+      <c r="L21" s="9">
+        <f t="shared" si="13"/>
+        <v>0.31876624745310189</v>
+      </c>
+      <c r="M21" s="9">
+        <f t="shared" si="13"/>
+        <v>0.2545552028570548</v>
+      </c>
+      <c r="N21" s="9" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
       <c r="Q21" s="3"/>
@@ -2290,10 +2571,22 @@
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
-      <c r="N22" s="3"/>
+      <c r="K22" s="9">
+        <f t="shared" si="13"/>
+        <v>0.28730420445177263</v>
+      </c>
+      <c r="L22" s="9">
+        <f t="shared" si="13"/>
+        <v>0.22725570947210771</v>
+      </c>
+      <c r="M22" s="9">
+        <f t="shared" si="13"/>
+        <v>0.38126068770482946</v>
+      </c>
+      <c r="N22" s="9" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
@@ -2348,33 +2641,45 @@
       <c r="BN22" s="6"/>
     </row>
     <row r="23" spans="2:66" x14ac:dyDescent="0.2">
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="9" t="e">
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="13" t="e">
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H23" s="9" t="e">
+      <c r="H23" s="13" t="e">
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I23" s="9">
+      <c r="I23" s="13">
         <f t="shared" si="14"/>
         <v>0.19972758397727408</v>
       </c>
-      <c r="J23" s="9" t="e">
+      <c r="J23" s="13" t="e">
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
-      <c r="N23" s="3"/>
+      <c r="K23" s="13">
+        <f t="shared" si="13"/>
+        <v>0.27580501463662976</v>
+      </c>
+      <c r="L23" s="13">
+        <f t="shared" si="13"/>
+        <v>0.30430667297681024</v>
+      </c>
+      <c r="M23" s="13">
+        <f t="shared" si="13"/>
+        <v>0.27464471411468994</v>
+      </c>
+      <c r="N23" s="13" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
@@ -2448,26 +2753,38 @@
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G24" s="9" t="e">
+      <c r="G24" s="9">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H24" s="9" t="e">
+        <v>0.60739012642986145</v>
+      </c>
+      <c r="H24" s="9">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
+        <v>0.6203189770252231</v>
       </c>
       <c r="I24" s="9">
         <f>+(I3-I6)/I3</f>
         <v>0.61061801133608129</v>
       </c>
       <c r="J24" s="9" t="e">
-        <f>+(J3-J6)/J3</f>
+        <f t="shared" ref="J24:N24" si="16">+(J3-J6)/J3</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="M24" s="3"/>
-      <c r="N24" s="3"/>
+      <c r="K24" s="9">
+        <f t="shared" si="16"/>
+        <v>0.60254062038404721</v>
+      </c>
+      <c r="L24" s="9">
+        <f t="shared" si="16"/>
+        <v>0.62317527970165154</v>
+      </c>
+      <c r="M24" s="9">
+        <f t="shared" si="16"/>
+        <v>0.61003295496155252</v>
+      </c>
+      <c r="N24" s="9" t="e">
+        <f t="shared" si="16"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
       <c r="Q24" s="3"/>
@@ -2526,41 +2843,53 @@
         <v>38</v>
       </c>
       <c r="C25" s="9" t="e">
-        <f t="shared" ref="C25:H25" si="16">+(C4-C7)/C4</f>
+        <f t="shared" ref="C25:H25" si="17">+(C4-C7)/C4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D25" s="9" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E25" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.80272701288029014</v>
       </c>
       <c r="F25" s="9" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G25" s="9" t="e">
-        <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H25" s="9" t="e">
-        <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+      <c r="G25" s="9">
+        <f t="shared" si="17"/>
+        <v>0.80090684253915922</v>
+      </c>
+      <c r="H25" s="9">
+        <f t="shared" si="17"/>
+        <v>0.80232122800449268</v>
       </c>
       <c r="I25" s="9">
         <f>+(I4-I7)/I4</f>
         <v>0.80539757391277089</v>
       </c>
       <c r="J25" s="9" t="e">
-        <f>+(J4-J7)/J4</f>
+        <f t="shared" ref="J25:N25" si="18">+(J4-J7)/J4</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3"/>
+      <c r="K25" s="9">
+        <f t="shared" si="18"/>
+        <v>0.82068523855267372</v>
+      </c>
+      <c r="L25" s="9">
+        <f t="shared" si="18"/>
+        <v>0.82031726662599158</v>
+      </c>
+      <c r="M25" s="9">
+        <f t="shared" si="18"/>
+        <v>0.81694402420574885</v>
+      </c>
+      <c r="N25" s="9" t="e">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="O25" s="3"/>
       <c r="P25" s="3"/>
       <c r="Q25" s="3"/>
@@ -2619,41 +2948,53 @@
         <v>39</v>
       </c>
       <c r="C26" s="9" t="e">
-        <f t="shared" ref="C26:H26" si="17">+C8/C5</f>
+        <f t="shared" ref="C26:H26" si="19">+C8/C5</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D26" s="9" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E26" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.62434347208530749</v>
       </c>
       <c r="F26" s="9" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G26" s="9" t="e">
-        <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H26" s="9" t="e">
-        <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
+      <c r="G26" s="9">
+        <f t="shared" si="19"/>
+        <v>0.63726613211149286</v>
+      </c>
+      <c r="H26" s="9">
+        <f t="shared" si="19"/>
+        <v>0.64907714150496931</v>
       </c>
       <c r="I26" s="9">
         <f>+I8/I5</f>
         <v>0.64150085922418021</v>
       </c>
       <c r="J26" s="9" t="e">
-        <f t="shared" ref="J26" si="18">+J8/J5</f>
+        <f t="shared" ref="J26:N26" si="20">+J8/J5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
-      <c r="N26" s="3"/>
+      <c r="K26" s="9">
+        <f t="shared" si="20"/>
+        <v>0.63652234636871508</v>
+      </c>
+      <c r="L26" s="9">
+        <f t="shared" si="20"/>
+        <v>0.65248548621190139</v>
+      </c>
+      <c r="M26" s="9">
+        <f t="shared" si="20"/>
+        <v>0.64558332972317301</v>
+      </c>
+      <c r="N26" s="9" t="e">
+        <f t="shared" si="20"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
       <c r="Q26" s="3"/>
@@ -2712,41 +3053,53 @@
         <v>40</v>
       </c>
       <c r="C27" s="9" t="e">
-        <f t="shared" ref="C27:H27" si="19">+C12/C5</f>
+        <f t="shared" ref="C27:H27" si="21">+C12/C5</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D27" s="9" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E27" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0.39927960801772283</v>
       </c>
       <c r="F27" s="9" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G27" s="9" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H27" s="9" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+      <c r="G27" s="9">
+        <f t="shared" si="21"/>
+        <v>0.42013491154384619</v>
+      </c>
+      <c r="H27" s="9">
+        <f t="shared" si="21"/>
+        <v>0.41386654046379573</v>
       </c>
       <c r="I27" s="9">
         <f>+I12/I5</f>
         <v>0.43361554466861341</v>
       </c>
       <c r="J27" s="9" t="e">
-        <f t="shared" ref="J27" si="20">+J12/J5</f>
+        <f t="shared" ref="J27:N27" si="22">+J12/J5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
-      <c r="N27" s="3"/>
+      <c r="K27" s="9">
+        <f t="shared" si="22"/>
+        <v>0.42837190742218673</v>
+      </c>
+      <c r="L27" s="9">
+        <f t="shared" si="22"/>
+        <v>0.44729680696661844</v>
+      </c>
+      <c r="M27" s="9">
+        <f t="shared" si="22"/>
+        <v>0.42377507256422486</v>
+      </c>
+      <c r="N27" s="9" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
       <c r="Q27" s="3"/>
@@ -2805,41 +3158,53 @@
         <v>41</v>
       </c>
       <c r="C28" s="9" t="e">
-        <f t="shared" ref="C28:H28" si="21">+C15/C14</f>
+        <f t="shared" ref="C28:H28" si="23">+C15/C14</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D28" s="9" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E28" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0.15388900094645552</v>
       </c>
       <c r="F28" s="9" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G28" s="9" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H28" s="9" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
+      <c r="G28" s="9">
+        <f t="shared" si="23"/>
+        <v>0.11773657996679582</v>
+      </c>
+      <c r="H28" s="9">
+        <f t="shared" si="23"/>
+        <v>0.13629283489096566</v>
       </c>
       <c r="I28" s="9">
         <f>+I15/I14</f>
         <v>0.15287175363287311</v>
       </c>
       <c r="J28" s="9" t="e">
-        <f t="shared" ref="J28" si="22">+J15/J14</f>
+        <f t="shared" ref="J28:N28" si="24">+J15/J14</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
-      <c r="N28" s="3"/>
+      <c r="K28" s="9">
+        <f t="shared" si="24"/>
+        <v>0.14785340314136125</v>
+      </c>
+      <c r="L28" s="9">
+        <f t="shared" si="24"/>
+        <v>0.17718940936863539</v>
+      </c>
+      <c r="M28" s="9">
+        <f t="shared" si="24"/>
+        <v>0.20805867607464482</v>
+      </c>
+      <c r="N28" s="9" t="e">
+        <f t="shared" si="24"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
       <c r="Q28" s="3"/>
